--- a/database/controller_excel/Resguardo_Pedro_Soler_Amaya.xlsx
+++ b/database/controller_excel/Resguardo_Pedro_Soler_Amaya.xlsx
@@ -38,7 +38,7 @@
     <t>Fecha:</t>
   </si>
   <si>
-    <t>24/04/2025</t>
+    <t>29/04/2025</t>
   </si>
   <si>
     <t>Nombre:</t>
@@ -50,7 +50,7 @@
     <t>Área:</t>
   </si>
   <si>
-    <t>Coordinador de Operaciones</t>
+    <t>Coordinador Operaciones</t>
   </si>
   <si>
     <t>Región:</t>
@@ -86,6 +86,21 @@
     <t>OBSERVACIONES</t>
   </si>
   <si>
+    <t>Laptop</t>
+  </si>
+  <si>
+    <t>DELL</t>
+  </si>
+  <si>
+    <t>Latitude 5520</t>
+  </si>
+  <si>
+    <t>GTDG2B3</t>
+  </si>
+  <si>
+    <t>DVZ-VH-TI-00128</t>
+  </si>
+  <si>
     <t>Desktop</t>
   </si>
   <si>
@@ -98,9 +113,6 @@
     <t>2UA4321Y3C</t>
   </si>
   <si>
-    <t>DELL</t>
-  </si>
-  <si>
     <t>Optiplex 790</t>
   </si>
   <si>
@@ -110,6 +122,240 @@
     <t>DVZ-VH-TI-00005</t>
   </si>
   <si>
+    <t>58PGKS1</t>
+  </si>
+  <si>
+    <t>815P7V1</t>
+  </si>
+  <si>
+    <t>DVZ-VH-TI-00052</t>
+  </si>
+  <si>
+    <t>Optiplex 7050</t>
+  </si>
+  <si>
+    <t>621MGL</t>
+  </si>
+  <si>
+    <t>DVZ-VH-TI-00171</t>
+  </si>
+  <si>
+    <t>Optiplex 780</t>
+  </si>
+  <si>
+    <t>2G3ZCP1</t>
+  </si>
+  <si>
+    <t>DVZ-VH-TI-00142</t>
+  </si>
+  <si>
+    <t>H6KZLP2</t>
+  </si>
+  <si>
+    <t>DVZ-VH-TI-00175</t>
+  </si>
+  <si>
+    <t>Optiplex Micro 7010</t>
+  </si>
+  <si>
+    <t>C7LNG04</t>
+  </si>
+  <si>
+    <t>DVZ-VH-TI-00185</t>
+  </si>
+  <si>
+    <t>Cargador Doking Station</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>CN-03XYY8-CH200-8BF-CB1G-A00</t>
+  </si>
+  <si>
+    <t>Monitor</t>
+  </si>
+  <si>
+    <t>EliteDisplay E231</t>
+  </si>
+  <si>
+    <t>6CM4250JLH</t>
+  </si>
+  <si>
+    <t>Telefono</t>
+  </si>
+  <si>
+    <t>Polycom</t>
+  </si>
+  <si>
+    <t>VVX 150</t>
+  </si>
+  <si>
+    <t>64167F7F6454</t>
+  </si>
+  <si>
+    <t>UPS</t>
+  </si>
+  <si>
+    <t>KOBLENZ</t>
+  </si>
+  <si>
+    <t>5216 R</t>
+  </si>
+  <si>
+    <t>21-06-25543</t>
+  </si>
+  <si>
+    <t>Teclado</t>
+  </si>
+  <si>
+    <t>WK118</t>
+  </si>
+  <si>
+    <t>CN-0J5K9F-LO300-87R-KOUL-A00</t>
+  </si>
+  <si>
+    <t>Mouse</t>
+  </si>
+  <si>
+    <t>CN-0J5K9F-LO300-87R-MOUL-A00</t>
+  </si>
+  <si>
+    <t>Camara Fotografica</t>
+  </si>
+  <si>
+    <t>NIKON</t>
+  </si>
+  <si>
+    <t>S2800</t>
+  </si>
+  <si>
+    <t>MIXIE</t>
+  </si>
+  <si>
+    <t>1909Wf</t>
+  </si>
+  <si>
+    <t>CN-0NKHGN-74261-261-1Y4M</t>
+  </si>
+  <si>
+    <t>22-04-04211</t>
+  </si>
+  <si>
+    <t>MS116t1</t>
+  </si>
+  <si>
+    <t>CN-065K5F-LO300-150-01E4</t>
+  </si>
+  <si>
+    <t>Pantalla TV</t>
+  </si>
+  <si>
+    <t>SONY</t>
+  </si>
+  <si>
+    <t>KDL-40EX600</t>
+  </si>
+  <si>
+    <t>KU-1156</t>
+  </si>
+  <si>
+    <t>BDMHE0C5Y6P0S8</t>
+  </si>
+  <si>
+    <t>Modem Router</t>
+  </si>
+  <si>
+    <t>SOYEA</t>
+  </si>
+  <si>
+    <t>B311-522</t>
+  </si>
+  <si>
+    <t>CEF7S22310012934</t>
+  </si>
+  <si>
+    <t>P1913b</t>
+  </si>
+  <si>
+    <t>CN-0NKHGN-74261-261-1WGM</t>
+  </si>
+  <si>
+    <t>Base para monitor</t>
+  </si>
+  <si>
+    <t>P190S</t>
+  </si>
+  <si>
+    <t>CN-03JKM1-14941-26R-0153</t>
+  </si>
+  <si>
+    <t>KU-0316</t>
+  </si>
+  <si>
+    <t>BDALC0NVB5X2F6</t>
+  </si>
+  <si>
+    <t>LOGITECH</t>
+  </si>
+  <si>
+    <t>M100</t>
+  </si>
+  <si>
+    <t>1849HS05N3H8</t>
+  </si>
+  <si>
+    <t>KB216t</t>
+  </si>
+  <si>
+    <t>CN-0F2JV2-LO300-0CE-00LY-A04</t>
+  </si>
+  <si>
+    <t>CN-065K5F-LO300-150-01FZ</t>
+  </si>
+  <si>
+    <t>22-04-4212</t>
+  </si>
+  <si>
+    <t>Desktop/Monitor</t>
+  </si>
+  <si>
+    <t>Optiplex 7490 AIO</t>
+  </si>
+  <si>
+    <t>HSYKTH3</t>
+  </si>
+  <si>
+    <t>DVZ-VH-TI-00068</t>
+  </si>
+  <si>
+    <t>Logitech</t>
+  </si>
+  <si>
+    <t>K120</t>
+  </si>
+  <si>
+    <t>1446MG00C678</t>
+  </si>
+  <si>
+    <t>SM-2022</t>
+  </si>
+  <si>
+    <t>FCMHH0C9Z7ZSCE</t>
+  </si>
+  <si>
+    <t>Switch</t>
+  </si>
+  <si>
+    <t>Tp-link</t>
+  </si>
+  <si>
+    <t>TL-SG108E</t>
+  </si>
+  <si>
+    <t>Y223002003264</t>
+  </si>
+  <si>
     <t>Cargador Laptop</t>
   </si>
   <si>
@@ -119,12 +365,132 @@
     <t>CN-0VT148-LOC00-16H-AKCY-A02</t>
   </si>
   <si>
+    <t>CN-0NKHGN-74261-261-1WKM</t>
+  </si>
+  <si>
+    <t>Base para Desktop</t>
+  </si>
+  <si>
+    <t>CN-03JKM1-14941-26R-0159</t>
+  </si>
+  <si>
+    <t>KB-212B</t>
+  </si>
+  <si>
+    <t>CN-0KHCC7-71616-26C-0LCM-A00</t>
+  </si>
+  <si>
+    <t>M90</t>
+  </si>
+  <si>
+    <t>1445HS016L28</t>
+  </si>
+  <si>
+    <t>Huawei</t>
+  </si>
+  <si>
+    <t>B311-521</t>
+  </si>
+  <si>
+    <t>XKRUT22121005389</t>
+  </si>
+  <si>
     <t>Backpack DELL</t>
   </si>
   <si>
     <t>N/A</t>
   </si>
   <si>
+    <t>Adaptador de Corriente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AC </t>
+  </si>
+  <si>
+    <t>PA-65W</t>
+  </si>
+  <si>
+    <t>E2720HS</t>
+  </si>
+  <si>
+    <t>D57P283</t>
+  </si>
+  <si>
+    <t>Mixie</t>
+  </si>
+  <si>
+    <t>X6</t>
+  </si>
+  <si>
+    <t>X2</t>
+  </si>
+  <si>
+    <t>TCL</t>
+  </si>
+  <si>
+    <t>43S3504</t>
+  </si>
+  <si>
+    <t>2402NMS001197A00325</t>
+  </si>
+  <si>
+    <t>Impresora</t>
+  </si>
+  <si>
+    <t>Epson</t>
+  </si>
+  <si>
+    <t>EcoTank L6270</t>
+  </si>
+  <si>
+    <t>X8G5094519</t>
+  </si>
+  <si>
+    <t>KYOCERA</t>
+  </si>
+  <si>
+    <t>ECOSYS M2635dw</t>
+  </si>
+  <si>
+    <t>VCA2412297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Desktop </t>
+  </si>
+  <si>
+    <t>5RVTG04</t>
+  </si>
+  <si>
+    <t>DVZ-VH-TI-00177</t>
+  </si>
+  <si>
+    <t>Cargador Desktop</t>
+  </si>
+  <si>
+    <t>LA90PM111</t>
+  </si>
+  <si>
+    <t>CN-07HRTX-LOC00-3AP-ADE5-A01</t>
+  </si>
+  <si>
+    <t>KB216t1</t>
+  </si>
+  <si>
+    <t>CN-019M93-LO300-3AL-0JQU-A04</t>
+  </si>
+  <si>
+    <t>CN-065K5F-LO300-36D-0AZV</t>
+  </si>
+  <si>
+    <t>Router</t>
+  </si>
+  <si>
+    <t>Teltonika</t>
+  </si>
+  <si>
+    <t>RUT950</t>
+  </si>
+  <si>
     <t>Docking Station</t>
   </si>
   <si>
@@ -132,372 +498,6 @@
   </si>
   <si>
     <t>TW-05FDDV-32070-81C-0EF2-A06</t>
-  </si>
-  <si>
-    <t>Cargador Doking Station</t>
-  </si>
-  <si>
-    <t>NA</t>
-  </si>
-  <si>
-    <t>CN-03XYY8-CH200-8BF-CB1G-A00</t>
-  </si>
-  <si>
-    <t>Monitor</t>
-  </si>
-  <si>
-    <t>EliteDisplay E231</t>
-  </si>
-  <si>
-    <t>6CM4250JLH</t>
-  </si>
-  <si>
-    <t>Telefono</t>
-  </si>
-  <si>
-    <t>Polycom</t>
-  </si>
-  <si>
-    <t>VVX 150</t>
-  </si>
-  <si>
-    <t>64167F7F6454</t>
-  </si>
-  <si>
-    <t>UPS</t>
-  </si>
-  <si>
-    <t>KOBLENZ</t>
-  </si>
-  <si>
-    <t>5216 R</t>
-  </si>
-  <si>
-    <t>21-06-25543</t>
-  </si>
-  <si>
-    <t>Teclado</t>
-  </si>
-  <si>
-    <t>WK118</t>
-  </si>
-  <si>
-    <t>CN-0J5K9F-LO300-87R-KOUL-A00</t>
-  </si>
-  <si>
-    <t>Mouse</t>
-  </si>
-  <si>
-    <t>CN-0J5K9F-LO300-87R-MOUL-A00</t>
-  </si>
-  <si>
-    <t>Camara Fotografica</t>
-  </si>
-  <si>
-    <t>NIKON</t>
-  </si>
-  <si>
-    <t>S2800</t>
-  </si>
-  <si>
-    <t>815P7V1</t>
-  </si>
-  <si>
-    <t>DVZ-VH-TI-00052</t>
-  </si>
-  <si>
-    <t>Optiplex 7050</t>
-  </si>
-  <si>
-    <t>621MGL</t>
-  </si>
-  <si>
-    <t>DVZ-VH-TI-00171</t>
-  </si>
-  <si>
-    <t>MIXIE</t>
-  </si>
-  <si>
-    <t>1909Wf</t>
-  </si>
-  <si>
-    <t>CN-0NKHGN-74261-261-1Y4M</t>
-  </si>
-  <si>
-    <t>22-04-04211</t>
-  </si>
-  <si>
-    <t>58PGKS1</t>
-  </si>
-  <si>
-    <t>MS116t1</t>
-  </si>
-  <si>
-    <t>CN-065K5F-LO300-150-01E4</t>
-  </si>
-  <si>
-    <t>Pantalla TV</t>
-  </si>
-  <si>
-    <t>SONY</t>
-  </si>
-  <si>
-    <t>KDL-40EX600</t>
-  </si>
-  <si>
-    <t>KU-1156</t>
-  </si>
-  <si>
-    <t>BDMHE0C5Y6P0S8</t>
-  </si>
-  <si>
-    <t>Modem Router</t>
-  </si>
-  <si>
-    <t>SOYEA</t>
-  </si>
-  <si>
-    <t>B311-522</t>
-  </si>
-  <si>
-    <t>CEF7S22310012934</t>
-  </si>
-  <si>
-    <t>Laptop</t>
-  </si>
-  <si>
-    <t>Latitude 5520</t>
-  </si>
-  <si>
-    <t>GTDG2B3</t>
-  </si>
-  <si>
-    <t>DVZ-VH-TI-00128</t>
-  </si>
-  <si>
-    <t>P1913b</t>
-  </si>
-  <si>
-    <t>CN-0NKHGN-74261-261-1WGM</t>
-  </si>
-  <si>
-    <t>Base para monitor</t>
-  </si>
-  <si>
-    <t>P190S</t>
-  </si>
-  <si>
-    <t>CN-03JKM1-14941-26R-0153</t>
-  </si>
-  <si>
-    <t>KU-0316</t>
-  </si>
-  <si>
-    <t>BDALC0NVB5X2F6</t>
-  </si>
-  <si>
-    <t>LOGITECH</t>
-  </si>
-  <si>
-    <t>M100</t>
-  </si>
-  <si>
-    <t>1849HS05N3H8</t>
-  </si>
-  <si>
-    <t>KB216t</t>
-  </si>
-  <si>
-    <t>CN-0F2JV2-LO300-0CE-00LY-A04</t>
-  </si>
-  <si>
-    <t>CN-065K5F-LO300-150-01FZ</t>
-  </si>
-  <si>
-    <t>22-04-4212</t>
-  </si>
-  <si>
-    <t>Desktop/Monitor</t>
-  </si>
-  <si>
-    <t>Optiplex 7490 AIO</t>
-  </si>
-  <si>
-    <t>HSYKTH3</t>
-  </si>
-  <si>
-    <t>DVZ-VH-TI-00068</t>
-  </si>
-  <si>
-    <t>Logitech</t>
-  </si>
-  <si>
-    <t>K120</t>
-  </si>
-  <si>
-    <t>1446MG00C678</t>
-  </si>
-  <si>
-    <t>SM-2022</t>
-  </si>
-  <si>
-    <t>FCMHH0C9Z7ZSCE</t>
-  </si>
-  <si>
-    <t>Switch</t>
-  </si>
-  <si>
-    <t>Tp-link</t>
-  </si>
-  <si>
-    <t>TL-SG108E</t>
-  </si>
-  <si>
-    <t>Y223002003264</t>
-  </si>
-  <si>
-    <t>Optiplex 780</t>
-  </si>
-  <si>
-    <t>2G3ZCP1</t>
-  </si>
-  <si>
-    <t>DVZ-VH-TI-00142</t>
-  </si>
-  <si>
-    <t>CN-0NKHGN-74261-261-1WKM</t>
-  </si>
-  <si>
-    <t>Base para Desktop</t>
-  </si>
-  <si>
-    <t>CN-03JKM1-14941-26R-0159</t>
-  </si>
-  <si>
-    <t>KB-212B</t>
-  </si>
-  <si>
-    <t>CN-0KHCC7-71616-26C-0LCM-A00</t>
-  </si>
-  <si>
-    <t>M90</t>
-  </si>
-  <si>
-    <t>1445HS016L28</t>
-  </si>
-  <si>
-    <t>Huawei</t>
-  </si>
-  <si>
-    <t>B311-521</t>
-  </si>
-  <si>
-    <t>XKRUT22121005389</t>
-  </si>
-  <si>
-    <t>H6KZLP2</t>
-  </si>
-  <si>
-    <t>DVZ-VH-TI-00175</t>
-  </si>
-  <si>
-    <t>Adaptador de Corriente</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AC </t>
-  </si>
-  <si>
-    <t>PA-65W</t>
-  </si>
-  <si>
-    <t>E2720HS</t>
-  </si>
-  <si>
-    <t>D57P283</t>
-  </si>
-  <si>
-    <t>Mixie</t>
-  </si>
-  <si>
-    <t>X6</t>
-  </si>
-  <si>
-    <t>X2</t>
-  </si>
-  <si>
-    <t>TCL</t>
-  </si>
-  <si>
-    <t>43S3504</t>
-  </si>
-  <si>
-    <t>2402NMS001197A00325</t>
-  </si>
-  <si>
-    <t>Impresora</t>
-  </si>
-  <si>
-    <t>Epson</t>
-  </si>
-  <si>
-    <t>EcoTank L6270</t>
-  </si>
-  <si>
-    <t>X8G5094519</t>
-  </si>
-  <si>
-    <t>KYOCERA</t>
-  </si>
-  <si>
-    <t>ECOSYS M2635dw</t>
-  </si>
-  <si>
-    <t>VCA2412297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Desktop </t>
-  </si>
-  <si>
-    <t>Optiplex Micro 7010</t>
-  </si>
-  <si>
-    <t>5RVTG04</t>
-  </si>
-  <si>
-    <t>DVZ-VH-TI-00177</t>
-  </si>
-  <si>
-    <t>Cargador Desktop</t>
-  </si>
-  <si>
-    <t>LA90PM111</t>
-  </si>
-  <si>
-    <t>CN-07HRTX-LOC00-3AP-ADE5-A01</t>
-  </si>
-  <si>
-    <t>KB216t1</t>
-  </si>
-  <si>
-    <t>CN-019M93-LO300-3AL-0JQU-A04</t>
-  </si>
-  <si>
-    <t>CN-065K5F-LO300-36D-0AZV</t>
-  </si>
-  <si>
-    <t>Router</t>
-  </si>
-  <si>
-    <t>Teltonika</t>
-  </si>
-  <si>
-    <t>RUT950</t>
-  </si>
-  <si>
-    <t>C7LNG04</t>
-  </si>
-  <si>
-    <t>DVZ-VH-TI-00185</t>
   </si>
   <si>
     <t>Fuente de alimentación</t>
@@ -1405,48 +1405,48 @@
       <c r="I19" s="38"/>
     </row>
     <row r="20" spans="1:10" customHeight="1" ht="15">
-      <c r="A20" s="38">
+      <c r="A20" s="22"/>
+      <c r="B20" s="22"/>
+      <c r="C20" s="22"/>
+      <c r="D20" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="E20" s="22"/>
+      <c r="F20" s="22"/>
+      <c r="G20" s="22"/>
+      <c r="H20" s="22"/>
+      <c r="I20" s="22"/>
+    </row>
+    <row r="21" spans="1:10" customHeight="1" ht="15">
+      <c r="A21" s="38">
         <v>2</v>
       </c>
-      <c r="B20" s="38" t="s">
-        <v>22</v>
-      </c>
-      <c r="C20" s="38" t="s">
-        <v>26</v>
-      </c>
-      <c r="D20" s="38" t="s">
+      <c r="B21" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="E20" s="38"/>
-      <c r="F20" s="38" t="s">
+      <c r="C21" s="38" t="s">
         <v>28</v>
       </c>
-      <c r="G20" s="38"/>
-      <c r="H20" s="38"/>
-      <c r="I20" s="38"/>
-    </row>
-    <row r="21" spans="1:10" customHeight="1" ht="15">
-      <c r="A21" s="22"/>
-      <c r="B21" s="22"/>
-      <c r="C21" s="22"/>
-      <c r="D21" s="22" t="s">
+      <c r="D21" s="38" t="s">
         <v>29</v>
       </c>
-      <c r="E21" s="22"/>
-      <c r="F21" s="22"/>
-      <c r="G21" s="22"/>
-      <c r="H21" s="22"/>
-      <c r="I21" s="22"/>
+      <c r="E21" s="38"/>
+      <c r="F21" s="38" t="s">
+        <v>30</v>
+      </c>
+      <c r="G21" s="38"/>
+      <c r="H21" s="38"/>
+      <c r="I21" s="38"/>
     </row>
     <row r="22" spans="1:10" customHeight="1" ht="15">
       <c r="A22" s="38">
         <v>3</v>
       </c>
       <c r="B22" s="38" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C22" s="38" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>31</v>
@@ -1460,42 +1460,34 @@
       <c r="I22" s="38"/>
     </row>
     <row r="23" spans="1:10" customHeight="1" ht="15">
-      <c r="A23" s="38">
-        <v>4</v>
-      </c>
-      <c r="B23" s="38" t="s">
+      <c r="A23" s="22"/>
+      <c r="B23" s="22"/>
+      <c r="C23" s="22"/>
+      <c r="D23" s="22" t="s">
         <v>33</v>
       </c>
-      <c r="C23" s="38" t="s">
-        <v>26</v>
-      </c>
-      <c r="D23" s="38" t="s">
-        <v>34</v>
-      </c>
-      <c r="E23" s="38"/>
-      <c r="F23" s="38" t="s">
-        <v>34</v>
-      </c>
-      <c r="G23" s="38"/>
-      <c r="H23" s="38"/>
-      <c r="I23" s="38"/>
+      <c r="E23" s="22"/>
+      <c r="F23" s="22"/>
+      <c r="G23" s="22"/>
+      <c r="H23" s="22"/>
+      <c r="I23" s="22"/>
     </row>
     <row r="24" spans="1:10" customHeight="1" ht="15">
       <c r="A24" s="38">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B24" s="38" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="C24" s="38" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D24" s="38" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="E24" s="38"/>
       <c r="F24" s="38" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G24" s="38"/>
       <c r="H24" s="38"/>
@@ -1503,235 +1495,211 @@
     </row>
     <row r="25" spans="1:10" customHeight="1" ht="15">
       <c r="A25" s="38">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B25" s="38" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="C25" s="38" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D25" s="38" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="E25" s="38"/>
       <c r="F25" s="38" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="G25" s="38"/>
       <c r="H25" s="38"/>
       <c r="I25" s="38"/>
     </row>
     <row r="26" spans="1:10" customHeight="1" ht="15">
-      <c r="A26" s="38">
-        <v>7</v>
-      </c>
-      <c r="B26" s="38" t="s">
-        <v>41</v>
-      </c>
-      <c r="C26" s="38" t="s">
-        <v>23</v>
-      </c>
-      <c r="D26" s="38" t="s">
-        <v>42</v>
-      </c>
-      <c r="E26" s="38"/>
-      <c r="F26" s="38" t="s">
-        <v>43</v>
-      </c>
-      <c r="G26" s="38"/>
-      <c r="H26" s="38"/>
-      <c r="I26" s="38"/>
+      <c r="A26" s="22"/>
+      <c r="B26" s="22"/>
+      <c r="C26" s="22"/>
+      <c r="D26" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="E26" s="22"/>
+      <c r="F26" s="22"/>
+      <c r="G26" s="22"/>
+      <c r="H26" s="22"/>
+      <c r="I26" s="22"/>
     </row>
     <row r="27" spans="1:10" customHeight="1" ht="15">
       <c r="A27" s="38">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B27" s="38" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="C27" s="38" t="s">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="D27" s="38" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="E27" s="38"/>
       <c r="F27" s="38" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="G27" s="38"/>
       <c r="H27" s="38"/>
       <c r="I27" s="38"/>
     </row>
     <row r="28" spans="1:10" customHeight="1" ht="15">
-      <c r="A28" s="38">
-        <v>9</v>
-      </c>
-      <c r="B28" s="38" t="s">
-        <v>48</v>
-      </c>
-      <c r="C28" s="38" t="s">
-        <v>49</v>
-      </c>
-      <c r="D28" s="38" t="s">
-        <v>50</v>
-      </c>
-      <c r="E28" s="38"/>
-      <c r="F28" s="38" t="s">
-        <v>51</v>
-      </c>
-      <c r="G28" s="38"/>
-      <c r="H28" s="38"/>
-      <c r="I28" s="38"/>
+      <c r="A28" s="22"/>
+      <c r="B28" s="22"/>
+      <c r="C28" s="22"/>
+      <c r="D28" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="E28" s="22"/>
+      <c r="F28" s="22"/>
+      <c r="G28" s="22"/>
+      <c r="H28" s="22"/>
+      <c r="I28" s="22"/>
     </row>
     <row r="29" spans="1:10" customHeight="1" ht="15">
       <c r="A29" s="38">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B29" s="38" t="s">
-        <v>52</v>
+        <v>27</v>
       </c>
       <c r="C29" s="38" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D29" s="38" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="E29" s="38"/>
       <c r="F29" s="38" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="G29" s="38"/>
       <c r="H29" s="38"/>
       <c r="I29" s="38"/>
     </row>
     <row r="30" spans="1:10" customHeight="1" ht="15">
-      <c r="A30" s="38">
-        <v>11</v>
-      </c>
-      <c r="B30" s="38" t="s">
-        <v>55</v>
-      </c>
-      <c r="C30" s="38" t="s">
-        <v>26</v>
-      </c>
-      <c r="D30" s="38" t="s">
-        <v>39</v>
-      </c>
-      <c r="E30" s="38"/>
-      <c r="F30" s="38" t="s">
-        <v>56</v>
-      </c>
-      <c r="G30" s="38"/>
-      <c r="H30" s="38"/>
-      <c r="I30" s="38"/>
+      <c r="A30" s="22"/>
+      <c r="B30" s="22"/>
+      <c r="C30" s="22"/>
+      <c r="D30" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="E30" s="22"/>
+      <c r="F30" s="22"/>
+      <c r="G30" s="22"/>
+      <c r="H30" s="22"/>
+      <c r="I30" s="22"/>
     </row>
     <row r="31" spans="1:10" customHeight="1" ht="15">
       <c r="A31" s="38">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B31" s="38" t="s">
-        <v>57</v>
+        <v>27</v>
       </c>
       <c r="C31" s="38" t="s">
-        <v>58</v>
+        <v>23</v>
       </c>
       <c r="D31" s="38" t="s">
-        <v>59</v>
+        <v>37</v>
       </c>
       <c r="E31" s="38"/>
-      <c r="F31" s="38">
-        <v>30008709</v>
+      <c r="F31" s="38" t="s">
+        <v>43</v>
       </c>
       <c r="G31" s="38"/>
       <c r="H31" s="38"/>
       <c r="I31" s="38"/>
     </row>
     <row r="32" spans="1:10" customHeight="1" ht="15">
-      <c r="A32" s="38">
-        <v>13</v>
-      </c>
-      <c r="B32" s="38" t="s">
-        <v>22</v>
-      </c>
-      <c r="C32" s="38" t="s">
-        <v>26</v>
-      </c>
-      <c r="D32" s="38" t="s">
+      <c r="A32" s="22"/>
+      <c r="B32" s="22"/>
+      <c r="C32" s="22"/>
+      <c r="D32" s="22" t="s">
+        <v>44</v>
+      </c>
+      <c r="E32" s="22"/>
+      <c r="F32" s="22"/>
+      <c r="G32" s="22"/>
+      <c r="H32" s="22"/>
+      <c r="I32" s="22"/>
+    </row>
+    <row r="33" spans="1:10" customHeight="1" ht="15">
+      <c r="A33" s="38">
+        <v>9</v>
+      </c>
+      <c r="B33" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="E32" s="38"/>
-      <c r="F32" s="38" t="s">
-        <v>60</v>
-      </c>
-      <c r="G32" s="38"/>
-      <c r="H32" s="38"/>
-      <c r="I32" s="38"/>
-    </row>
-    <row r="33" spans="1:10" customHeight="1" ht="15">
-      <c r="A33" s="22"/>
-      <c r="B33" s="22"/>
-      <c r="C33" s="22"/>
-      <c r="D33" s="22" t="s">
-        <v>61</v>
-      </c>
-      <c r="E33" s="22"/>
-      <c r="F33" s="22"/>
-      <c r="G33" s="22"/>
-      <c r="H33" s="22"/>
-      <c r="I33" s="22"/>
+      <c r="C33" s="38" t="s">
+        <v>23</v>
+      </c>
+      <c r="D33" s="38" t="s">
+        <v>45</v>
+      </c>
+      <c r="E33" s="38"/>
+      <c r="F33" s="38" t="s">
+        <v>46</v>
+      </c>
+      <c r="G33" s="38"/>
+      <c r="H33" s="38"/>
+      <c r="I33" s="38"/>
     </row>
     <row r="34" spans="1:10" customHeight="1" ht="15">
-      <c r="A34" s="38">
-        <v>14</v>
-      </c>
-      <c r="B34" s="38" t="s">
-        <v>22</v>
-      </c>
-      <c r="C34" s="38" t="s">
-        <v>26</v>
-      </c>
-      <c r="D34" s="38" t="s">
-        <v>62</v>
-      </c>
-      <c r="E34" s="38"/>
-      <c r="F34" s="38" t="s">
-        <v>63</v>
-      </c>
-      <c r="G34" s="38"/>
-      <c r="H34" s="38"/>
-      <c r="I34" s="38"/>
+      <c r="A34" s="22"/>
+      <c r="B34" s="22"/>
+      <c r="C34" s="22"/>
+      <c r="D34" s="22" t="s">
+        <v>47</v>
+      </c>
+      <c r="E34" s="22"/>
+      <c r="F34" s="22"/>
+      <c r="G34" s="22"/>
+      <c r="H34" s="22"/>
+      <c r="I34" s="22"/>
     </row>
     <row r="35" spans="1:10" customHeight="1" ht="15">
-      <c r="A35" s="22"/>
-      <c r="B35" s="22"/>
-      <c r="C35" s="22"/>
-      <c r="D35" s="22" t="s">
-        <v>64</v>
-      </c>
-      <c r="E35" s="22"/>
-      <c r="F35" s="22"/>
-      <c r="G35" s="22"/>
-      <c r="H35" s="22"/>
-      <c r="I35" s="22"/>
+      <c r="A35" s="38">
+        <v>10</v>
+      </c>
+      <c r="B35" s="38" t="s">
+        <v>48</v>
+      </c>
+      <c r="C35" s="38" t="s">
+        <v>23</v>
+      </c>
+      <c r="D35" s="38" t="s">
+        <v>49</v>
+      </c>
+      <c r="E35" s="38"/>
+      <c r="F35" s="38" t="s">
+        <v>50</v>
+      </c>
+      <c r="G35" s="38"/>
+      <c r="H35" s="38"/>
+      <c r="I35" s="38"/>
     </row>
     <row r="36" spans="1:10" customHeight="1" ht="15">
       <c r="A36" s="38">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B36" s="38" t="s">
+        <v>51</v>
+      </c>
+      <c r="C36" s="38" t="s">
+        <v>28</v>
+      </c>
+      <c r="D36" s="38" t="s">
         <v>52</v>
       </c>
-      <c r="C36" s="38" t="s">
-        <v>65</v>
-      </c>
-      <c r="D36" s="38" t="s">
-        <v>39</v>
-      </c>
       <c r="E36" s="38"/>
-      <c r="F36" s="38">
-        <v>970344731196</v>
+      <c r="F36" s="38" t="s">
+        <v>53</v>
       </c>
       <c r="G36" s="38"/>
       <c r="H36" s="38"/>
@@ -1739,20 +1707,20 @@
     </row>
     <row r="37" spans="1:10" customHeight="1" ht="15">
       <c r="A37" s="38">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B37" s="38" t="s">
+        <v>54</v>
+      </c>
+      <c r="C37" s="38" t="s">
         <v>55</v>
       </c>
-      <c r="C37" s="38" t="s">
-        <v>65</v>
-      </c>
       <c r="D37" s="38" t="s">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="E37" s="38"/>
-      <c r="F37" s="38">
-        <v>974094311684</v>
+      <c r="F37" s="38" t="s">
+        <v>57</v>
       </c>
       <c r="G37" s="38"/>
       <c r="H37" s="38"/>
@@ -1760,20 +1728,20 @@
     </row>
     <row r="38" spans="1:10" customHeight="1" ht="15">
       <c r="A38" s="38">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B38" s="38" t="s">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="C38" s="38" t="s">
-        <v>26</v>
+        <v>59</v>
       </c>
       <c r="D38" s="38" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="E38" s="38"/>
       <c r="F38" s="38" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="G38" s="38"/>
       <c r="H38" s="38"/>
@@ -1781,20 +1749,20 @@
     </row>
     <row r="39" spans="1:10" customHeight="1" ht="15">
       <c r="A39" s="38">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B39" s="38" t="s">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="C39" s="38" t="s">
-        <v>49</v>
+        <v>23</v>
       </c>
       <c r="D39" s="38" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="E39" s="38"/>
       <c r="F39" s="38" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="G39" s="38"/>
       <c r="H39" s="38"/>
@@ -1802,20 +1770,20 @@
     </row>
     <row r="40" spans="1:10" customHeight="1" ht="15">
       <c r="A40" s="38">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B40" s="38" t="s">
-        <v>22</v>
+        <v>65</v>
       </c>
       <c r="C40" s="38" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D40" s="38" t="s">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="E40" s="38"/>
       <c r="F40" s="38" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="G40" s="38"/>
       <c r="H40" s="38"/>
@@ -1823,20 +1791,20 @@
     </row>
     <row r="41" spans="1:10" customHeight="1" ht="15">
       <c r="A41" s="38">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B41" s="38" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="C41" s="38" t="s">
-        <v>26</v>
+        <v>68</v>
       </c>
       <c r="D41" s="38" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E41" s="38"/>
-      <c r="F41" s="38" t="s">
-        <v>71</v>
+      <c r="F41" s="38">
+        <v>30008709</v>
       </c>
       <c r="G41" s="38"/>
       <c r="H41" s="38"/>
@@ -1844,20 +1812,20 @@
     </row>
     <row r="42" spans="1:10" customHeight="1" ht="15">
       <c r="A42" s="38">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B42" s="38" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="C42" s="38" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D42" s="38" t="s">
-        <v>74</v>
+        <v>49</v>
       </c>
       <c r="E42" s="38"/>
       <c r="F42" s="38">
-        <v>1014708</v>
+        <v>970344731196</v>
       </c>
       <c r="G42" s="38"/>
       <c r="H42" s="38"/>
@@ -1865,20 +1833,20 @@
     </row>
     <row r="43" spans="1:10" customHeight="1" ht="15">
       <c r="A43" s="38">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B43" s="38" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="C43" s="38" t="s">
-        <v>23</v>
+        <v>70</v>
       </c>
       <c r="D43" s="38" t="s">
-        <v>75</v>
+        <v>49</v>
       </c>
       <c r="E43" s="38"/>
-      <c r="F43" s="38" t="s">
-        <v>76</v>
+      <c r="F43" s="38">
+        <v>974094311684</v>
       </c>
       <c r="G43" s="38"/>
       <c r="H43" s="38"/>
@@ -1886,20 +1854,20 @@
     </row>
     <row r="44" spans="1:10" customHeight="1" ht="15">
       <c r="A44" s="38">
+        <v>19</v>
+      </c>
+      <c r="B44" s="38" t="s">
+        <v>51</v>
+      </c>
+      <c r="C44" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="B44" s="38" t="s">
-        <v>77</v>
-      </c>
-      <c r="C44" s="38" t="s">
-        <v>78</v>
-      </c>
       <c r="D44" s="38" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="E44" s="38"/>
       <c r="F44" s="38" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="G44" s="38"/>
       <c r="H44" s="38"/>
@@ -1907,54 +1875,62 @@
     </row>
     <row r="45" spans="1:10" customHeight="1" ht="15">
       <c r="A45" s="38">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B45" s="38" t="s">
-        <v>81</v>
+        <v>58</v>
       </c>
       <c r="C45" s="38" t="s">
-        <v>26</v>
+        <v>59</v>
       </c>
       <c r="D45" s="38" t="s">
-        <v>82</v>
+        <v>60</v>
       </c>
       <c r="E45" s="38"/>
       <c r="F45" s="38" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="G45" s="38"/>
       <c r="H45" s="38"/>
       <c r="I45" s="38"/>
     </row>
     <row r="46" spans="1:10" customHeight="1" ht="15">
-      <c r="A46" s="22"/>
-      <c r="B46" s="22"/>
-      <c r="C46" s="22"/>
-      <c r="D46" s="22" t="s">
-        <v>84</v>
-      </c>
-      <c r="E46" s="22"/>
-      <c r="F46" s="22"/>
-      <c r="G46" s="22"/>
-      <c r="H46" s="22"/>
-      <c r="I46" s="22"/>
+      <c r="A46" s="38">
+        <v>21</v>
+      </c>
+      <c r="B46" s="38" t="s">
+        <v>65</v>
+      </c>
+      <c r="C46" s="38" t="s">
+        <v>23</v>
+      </c>
+      <c r="D46" s="38" t="s">
+        <v>74</v>
+      </c>
+      <c r="E46" s="38"/>
+      <c r="F46" s="38" t="s">
+        <v>75</v>
+      </c>
+      <c r="G46" s="38"/>
+      <c r="H46" s="38"/>
+      <c r="I46" s="38"/>
     </row>
     <row r="47" spans="1:10" customHeight="1" ht="15">
       <c r="A47" s="38">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B47" s="38" t="s">
-        <v>41</v>
+        <v>76</v>
       </c>
       <c r="C47" s="38" t="s">
-        <v>26</v>
+        <v>77</v>
       </c>
       <c r="D47" s="38" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="E47" s="38"/>
-      <c r="F47" s="38" t="s">
-        <v>86</v>
+      <c r="F47" s="38">
+        <v>1014708</v>
       </c>
       <c r="G47" s="38"/>
       <c r="H47" s="38"/>
@@ -1962,20 +1938,20 @@
     </row>
     <row r="48" spans="1:10" customHeight="1" ht="15">
       <c r="A48" s="38">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B48" s="38" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="C48" s="38" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D48" s="38" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="E48" s="38"/>
       <c r="F48" s="38" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G48" s="38"/>
       <c r="H48" s="38"/>
@@ -1983,20 +1959,20 @@
     </row>
     <row r="49" spans="1:10" customHeight="1" ht="15">
       <c r="A49" s="38">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B49" s="38" t="s">
-        <v>52</v>
+        <v>81</v>
       </c>
       <c r="C49" s="38" t="s">
-        <v>23</v>
+        <v>82</v>
       </c>
       <c r="D49" s="38" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="E49" s="38"/>
       <c r="F49" s="38" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="G49" s="38"/>
       <c r="H49" s="38"/>
@@ -2004,20 +1980,20 @@
     </row>
     <row r="50" spans="1:10" customHeight="1" ht="15">
       <c r="A50" s="38">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B50" s="38" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C50" s="38" t="s">
-        <v>92</v>
+        <v>23</v>
       </c>
       <c r="D50" s="38" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="E50" s="38"/>
       <c r="F50" s="38" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="G50" s="38"/>
       <c r="H50" s="38"/>
@@ -2025,20 +2001,20 @@
     </row>
     <row r="51" spans="1:10" customHeight="1" ht="15">
       <c r="A51" s="38">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B51" s="38" t="s">
-        <v>52</v>
+        <v>87</v>
       </c>
       <c r="C51" s="38" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D51" s="38" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="E51" s="38"/>
       <c r="F51" s="38" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="G51" s="38"/>
       <c r="H51" s="38"/>
@@ -2046,20 +2022,20 @@
     </row>
     <row r="52" spans="1:10" customHeight="1" ht="15">
       <c r="A52" s="38">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B52" s="38" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="C52" s="38" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D52" s="38" t="s">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="E52" s="38"/>
       <c r="F52" s="38" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="G52" s="38"/>
       <c r="H52" s="38"/>
@@ -2067,20 +2043,20 @@
     </row>
     <row r="53" spans="1:10" customHeight="1" ht="15">
       <c r="A53" s="38">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B53" s="38" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="C53" s="38" t="s">
-        <v>49</v>
+        <v>92</v>
       </c>
       <c r="D53" s="38" t="s">
-        <v>50</v>
+        <v>93</v>
       </c>
       <c r="E53" s="38"/>
       <c r="F53" s="38" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="G53" s="38"/>
       <c r="H53" s="38"/>
@@ -2088,54 +2064,62 @@
     </row>
     <row r="54" spans="1:10" customHeight="1" ht="15">
       <c r="A54" s="38">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B54" s="38" t="s">
-        <v>99</v>
+        <v>62</v>
       </c>
       <c r="C54" s="38" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D54" s="38" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E54" s="38"/>
       <c r="F54" s="38" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="G54" s="38"/>
       <c r="H54" s="38"/>
       <c r="I54" s="38"/>
     </row>
     <row r="55" spans="1:10" customHeight="1" ht="15">
-      <c r="A55" s="22"/>
-      <c r="B55" s="22"/>
-      <c r="C55" s="22"/>
-      <c r="D55" s="22" t="s">
-        <v>102</v>
-      </c>
-      <c r="E55" s="22"/>
-      <c r="F55" s="22"/>
-      <c r="G55" s="22"/>
-      <c r="H55" s="22"/>
-      <c r="I55" s="22"/>
+      <c r="A55" s="38">
+        <v>30</v>
+      </c>
+      <c r="B55" s="38" t="s">
+        <v>65</v>
+      </c>
+      <c r="C55" s="38" t="s">
+        <v>23</v>
+      </c>
+      <c r="D55" s="38" t="s">
+        <v>74</v>
+      </c>
+      <c r="E55" s="38"/>
+      <c r="F55" s="38" t="s">
+        <v>97</v>
+      </c>
+      <c r="G55" s="38"/>
+      <c r="H55" s="38"/>
+      <c r="I55" s="38"/>
     </row>
     <row r="56" spans="1:10" customHeight="1" ht="15">
       <c r="A56" s="38">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B56" s="38" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="C56" s="38" t="s">
-        <v>103</v>
+        <v>59</v>
       </c>
       <c r="D56" s="38" t="s">
-        <v>104</v>
+        <v>60</v>
       </c>
       <c r="E56" s="38"/>
       <c r="F56" s="38" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="G56" s="38"/>
       <c r="H56" s="38"/>
@@ -2143,96 +2127,96 @@
     </row>
     <row r="57" spans="1:10" customHeight="1" ht="15">
       <c r="A57" s="38">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B57" s="38" t="s">
-        <v>55</v>
+        <v>99</v>
       </c>
       <c r="C57" s="38" t="s">
         <v>23</v>
       </c>
       <c r="D57" s="38" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="E57" s="38"/>
       <c r="F57" s="38" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="G57" s="38"/>
       <c r="H57" s="38"/>
       <c r="I57" s="38"/>
     </row>
     <row r="58" spans="1:10" customHeight="1" ht="15">
-      <c r="A58" s="38">
-        <v>35</v>
-      </c>
-      <c r="B58" s="38" t="s">
-        <v>108</v>
-      </c>
-      <c r="C58" s="38" t="s">
-        <v>109</v>
-      </c>
-      <c r="D58" s="38" t="s">
-        <v>110</v>
-      </c>
-      <c r="E58" s="38"/>
-      <c r="F58" s="38" t="s">
-        <v>111</v>
-      </c>
-      <c r="G58" s="38"/>
-      <c r="H58" s="38"/>
-      <c r="I58" s="38"/>
+      <c r="A58" s="22"/>
+      <c r="B58" s="22"/>
+      <c r="C58" s="22"/>
+      <c r="D58" s="22" t="s">
+        <v>102</v>
+      </c>
+      <c r="E58" s="22"/>
+      <c r="F58" s="22"/>
+      <c r="G58" s="22"/>
+      <c r="H58" s="22"/>
+      <c r="I58" s="22"/>
     </row>
     <row r="59" spans="1:10" customHeight="1" ht="15">
       <c r="A59" s="38">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B59" s="38" t="s">
-        <v>22</v>
+        <v>62</v>
       </c>
       <c r="C59" s="38" t="s">
-        <v>26</v>
+        <v>103</v>
       </c>
       <c r="D59" s="38" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="E59" s="38"/>
       <c r="F59" s="38" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="G59" s="38"/>
       <c r="H59" s="38"/>
       <c r="I59" s="38"/>
     </row>
     <row r="60" spans="1:10" customHeight="1" ht="15">
-      <c r="A60" s="22"/>
-      <c r="B60" s="22"/>
-      <c r="C60" s="22"/>
-      <c r="D60" s="22" t="s">
-        <v>114</v>
-      </c>
-      <c r="E60" s="22"/>
-      <c r="F60" s="22"/>
-      <c r="G60" s="22"/>
-      <c r="H60" s="22"/>
-      <c r="I60" s="22"/>
+      <c r="A60" s="38">
+        <v>34</v>
+      </c>
+      <c r="B60" s="38" t="s">
+        <v>65</v>
+      </c>
+      <c r="C60" s="38" t="s">
+        <v>28</v>
+      </c>
+      <c r="D60" s="38" t="s">
+        <v>106</v>
+      </c>
+      <c r="E60" s="38"/>
+      <c r="F60" s="38" t="s">
+        <v>107</v>
+      </c>
+      <c r="G60" s="38"/>
+      <c r="H60" s="38"/>
+      <c r="I60" s="38"/>
     </row>
     <row r="61" spans="1:10" customHeight="1" ht="15">
       <c r="A61" s="38">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B61" s="38" t="s">
-        <v>41</v>
+        <v>108</v>
       </c>
       <c r="C61" s="38" t="s">
-        <v>26</v>
+        <v>109</v>
       </c>
       <c r="D61" s="38" t="s">
-        <v>85</v>
+        <v>110</v>
       </c>
       <c r="E61" s="38"/>
       <c r="F61" s="38" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="G61" s="38"/>
       <c r="H61" s="38"/>
@@ -2240,20 +2224,20 @@
     </row>
     <row r="62" spans="1:10" customHeight="1" ht="15">
       <c r="A62" s="38">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B62" s="38" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="C62" s="38" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D62" s="38" t="s">
-        <v>88</v>
+        <v>113</v>
       </c>
       <c r="E62" s="38"/>
       <c r="F62" s="38" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="G62" s="38"/>
       <c r="H62" s="38"/>
@@ -2261,20 +2245,20 @@
     </row>
     <row r="63" spans="1:10" customHeight="1" ht="15">
       <c r="A63" s="38">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B63" s="38" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C63" s="38" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D63" s="38" t="s">
-        <v>118</v>
+        <v>85</v>
       </c>
       <c r="E63" s="38"/>
       <c r="F63" s="38" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="G63" s="38"/>
       <c r="H63" s="38"/>
@@ -2282,20 +2266,20 @@
     </row>
     <row r="64" spans="1:10" customHeight="1" ht="15">
       <c r="A64" s="38">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B64" s="38" t="s">
-        <v>55</v>
+        <v>116</v>
       </c>
       <c r="C64" s="38" t="s">
-        <v>103</v>
+        <v>23</v>
       </c>
       <c r="D64" s="38" t="s">
-        <v>120</v>
+        <v>88</v>
       </c>
       <c r="E64" s="38"/>
       <c r="F64" s="38" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="G64" s="38"/>
       <c r="H64" s="38"/>
@@ -2303,39 +2287,41 @@
     </row>
     <row r="65" spans="1:10" customHeight="1" ht="15">
       <c r="A65" s="38">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B65" s="38" t="s">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="C65" s="38" t="s">
-        <v>49</v>
+        <v>23</v>
       </c>
       <c r="D65" s="38" t="s">
-        <v>50</v>
+        <v>118</v>
       </c>
       <c r="E65" s="38"/>
-      <c r="F65" s="38"/>
+      <c r="F65" s="38" t="s">
+        <v>119</v>
+      </c>
       <c r="G65" s="38"/>
       <c r="H65" s="38"/>
       <c r="I65" s="38"/>
     </row>
     <row r="66" spans="1:10" customHeight="1" ht="15">
       <c r="A66" s="38">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B66" s="38" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="C66" s="38" t="s">
-        <v>122</v>
+        <v>103</v>
       </c>
       <c r="D66" s="38" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="E66" s="38"/>
       <c r="F66" s="38" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="G66" s="38"/>
       <c r="H66" s="38"/>
@@ -2343,54 +2329,60 @@
     </row>
     <row r="67" spans="1:10" customHeight="1" ht="15">
       <c r="A67" s="38">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B67" s="38" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="C67" s="38" t="s">
-        <v>26</v>
+        <v>59</v>
       </c>
       <c r="D67" s="38" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E67" s="38"/>
-      <c r="F67" s="38" t="s">
-        <v>125</v>
-      </c>
+      <c r="F67" s="38"/>
       <c r="G67" s="38"/>
       <c r="H67" s="38"/>
       <c r="I67" s="38"/>
     </row>
     <row r="68" spans="1:10" customHeight="1" ht="15">
-      <c r="A68" s="22"/>
-      <c r="B68" s="22"/>
-      <c r="C68" s="22"/>
-      <c r="D68" s="22" t="s">
-        <v>126</v>
-      </c>
-      <c r="E68" s="22"/>
-      <c r="F68" s="22"/>
-      <c r="G68" s="22"/>
-      <c r="H68" s="22"/>
-      <c r="I68" s="22"/>
+      <c r="A68" s="38">
+        <v>42</v>
+      </c>
+      <c r="B68" s="38" t="s">
+        <v>81</v>
+      </c>
+      <c r="C68" s="38" t="s">
+        <v>122</v>
+      </c>
+      <c r="D68" s="38" t="s">
+        <v>123</v>
+      </c>
+      <c r="E68" s="38"/>
+      <c r="F68" s="38" t="s">
+        <v>124</v>
+      </c>
+      <c r="G68" s="38"/>
+      <c r="H68" s="38"/>
+      <c r="I68" s="38"/>
     </row>
     <row r="69" spans="1:10" customHeight="1" ht="15">
       <c r="A69" s="38">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B69" s="38" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C69" s="38" t="s">
-        <v>128</v>
+        <v>23</v>
       </c>
       <c r="D69" s="38" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="E69" s="38"/>
-      <c r="F69" s="38">
-        <v>48511953340</v>
+      <c r="F69" s="38" t="s">
+        <v>126</v>
       </c>
       <c r="G69" s="38"/>
       <c r="H69" s="38"/>
@@ -2398,20 +2390,20 @@
     </row>
     <row r="70" spans="1:10" customHeight="1" ht="15">
       <c r="A70" s="38">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B70" s="38" t="s">
-        <v>41</v>
+        <v>127</v>
       </c>
       <c r="C70" s="38" t="s">
-        <v>26</v>
+        <v>128</v>
       </c>
       <c r="D70" s="38" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E70" s="38"/>
-      <c r="F70" s="38" t="s">
-        <v>131</v>
+      <c r="F70" s="38">
+        <v>48511953340</v>
       </c>
       <c r="G70" s="38"/>
       <c r="H70" s="38"/>
@@ -2419,20 +2411,20 @@
     </row>
     <row r="71" spans="1:10" customHeight="1" ht="15">
       <c r="A71" s="38">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B71" s="38" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C71" s="38" t="s">
-        <v>132</v>
+        <v>23</v>
       </c>
       <c r="D71" s="38" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="E71" s="38"/>
-      <c r="F71" s="38">
-        <v>970344731196</v>
+      <c r="F71" s="38" t="s">
+        <v>131</v>
       </c>
       <c r="G71" s="38"/>
       <c r="H71" s="38"/>
@@ -2440,20 +2432,20 @@
     </row>
     <row r="72" spans="1:10" customHeight="1" ht="15">
       <c r="A72" s="38">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B72" s="38" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="C72" s="38" t="s">
         <v>132</v>
       </c>
       <c r="D72" s="38" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E72" s="38"/>
       <c r="F72" s="38">
-        <v>974094311684</v>
+        <v>970344731196</v>
       </c>
       <c r="G72" s="38"/>
       <c r="H72" s="38"/>
@@ -2461,20 +2453,20 @@
     </row>
     <row r="73" spans="1:10" customHeight="1" ht="15">
       <c r="A73" s="38">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B73" s="38" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="C73" s="38" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D73" s="38" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E73" s="38"/>
-      <c r="F73" s="38" t="s">
-        <v>137</v>
+      <c r="F73" s="38">
+        <v>974094311684</v>
       </c>
       <c r="G73" s="38"/>
       <c r="H73" s="38"/>
@@ -2482,20 +2474,20 @@
     </row>
     <row r="74" spans="1:10" customHeight="1" ht="15">
       <c r="A74" s="38">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B74" s="38" t="s">
-        <v>138</v>
+        <v>76</v>
       </c>
       <c r="C74" s="38" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="D74" s="38" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="E74" s="38"/>
       <c r="F74" s="38" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="G74" s="38"/>
       <c r="H74" s="38"/>
@@ -2503,20 +2495,20 @@
     </row>
     <row r="75" spans="1:10" customHeight="1" ht="15">
       <c r="A75" s="38">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B75" s="38" t="s">
-        <v>72</v>
+        <v>138</v>
       </c>
       <c r="C75" s="38" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="D75" s="38" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="E75" s="38"/>
       <c r="F75" s="38" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="G75" s="38"/>
       <c r="H75" s="38"/>
@@ -2524,20 +2516,20 @@
     </row>
     <row r="76" spans="1:10" customHeight="1" ht="15">
       <c r="A76" s="38">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B76" s="38" t="s">
-        <v>138</v>
+        <v>76</v>
       </c>
       <c r="C76" s="38" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="D76" s="38" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="E76" s="38"/>
       <c r="F76" s="38" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="G76" s="38"/>
       <c r="H76" s="38"/>
@@ -2545,94 +2537,94 @@
     </row>
     <row r="77" spans="1:10" customHeight="1" ht="15">
       <c r="A77" s="38">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B77" s="38" t="s">
-        <v>48</v>
+        <v>138</v>
       </c>
       <c r="C77" s="38" t="s">
-        <v>49</v>
+        <v>142</v>
       </c>
       <c r="D77" s="38" t="s">
-        <v>50</v>
+        <v>143</v>
       </c>
       <c r="E77" s="38"/>
-      <c r="F77" s="38"/>
+      <c r="F77" s="38" t="s">
+        <v>144</v>
+      </c>
       <c r="G77" s="38"/>
       <c r="H77" s="38"/>
       <c r="I77" s="38"/>
     </row>
     <row r="78" spans="1:10" customHeight="1" ht="15">
       <c r="A78" s="38">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B78" s="38" t="s">
-        <v>145</v>
+        <v>58</v>
       </c>
       <c r="C78" s="38" t="s">
-        <v>26</v>
+        <v>59</v>
       </c>
       <c r="D78" s="38" t="s">
-        <v>146</v>
+        <v>60</v>
       </c>
       <c r="E78" s="38"/>
-      <c r="F78" s="38" t="s">
-        <v>147</v>
-      </c>
+      <c r="F78" s="38"/>
       <c r="G78" s="38"/>
       <c r="H78" s="38"/>
       <c r="I78" s="38"/>
     </row>
     <row r="79" spans="1:10" customHeight="1" ht="15">
-      <c r="A79" s="22"/>
-      <c r="B79" s="22"/>
-      <c r="C79" s="22"/>
-      <c r="D79" s="22" t="s">
-        <v>148</v>
-      </c>
-      <c r="E79" s="22"/>
-      <c r="F79" s="22"/>
-      <c r="G79" s="22"/>
-      <c r="H79" s="22"/>
-      <c r="I79" s="22"/>
+      <c r="A79" s="38">
+        <v>53</v>
+      </c>
+      <c r="B79" s="38" t="s">
+        <v>145</v>
+      </c>
+      <c r="C79" s="38" t="s">
+        <v>23</v>
+      </c>
+      <c r="D79" s="38" t="s">
+        <v>45</v>
+      </c>
+      <c r="E79" s="38"/>
+      <c r="F79" s="38" t="s">
+        <v>146</v>
+      </c>
+      <c r="G79" s="38"/>
+      <c r="H79" s="38"/>
+      <c r="I79" s="38"/>
     </row>
     <row r="80" spans="1:10" customHeight="1" ht="15">
-      <c r="A80" s="38">
-        <v>54</v>
-      </c>
-      <c r="B80" s="38" t="s">
-        <v>149</v>
-      </c>
-      <c r="C80" s="38" t="s">
-        <v>26</v>
-      </c>
-      <c r="D80" s="38" t="s">
-        <v>150</v>
-      </c>
-      <c r="E80" s="38"/>
-      <c r="F80" s="38" t="s">
-        <v>151</v>
-      </c>
-      <c r="G80" s="38"/>
-      <c r="H80" s="38"/>
-      <c r="I80" s="38"/>
+      <c r="A80" s="22"/>
+      <c r="B80" s="22"/>
+      <c r="C80" s="22"/>
+      <c r="D80" s="22" t="s">
+        <v>147</v>
+      </c>
+      <c r="E80" s="22"/>
+      <c r="F80" s="22"/>
+      <c r="G80" s="22"/>
+      <c r="H80" s="22"/>
+      <c r="I80" s="22"/>
     </row>
     <row r="81" spans="1:10" customHeight="1" ht="15">
       <c r="A81" s="38">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B81" s="38" t="s">
-        <v>52</v>
+        <v>148</v>
       </c>
       <c r="C81" s="38" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D81" s="38" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="E81" s="38"/>
       <c r="F81" s="38" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="G81" s="38"/>
       <c r="H81" s="38"/>
@@ -2640,20 +2632,20 @@
     </row>
     <row r="82" spans="1:10" customHeight="1" ht="15">
       <c r="A82" s="38">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B82" s="38" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="C82" s="38" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D82" s="38" t="s">
-        <v>70</v>
+        <v>151</v>
       </c>
       <c r="E82" s="38"/>
       <c r="F82" s="38" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="G82" s="38"/>
       <c r="H82" s="38"/>
@@ -2661,20 +2653,20 @@
     </row>
     <row r="83" spans="1:10" customHeight="1" ht="15">
       <c r="A83" s="38">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B83" s="38" t="s">
-        <v>155</v>
+        <v>65</v>
       </c>
       <c r="C83" s="38" t="s">
-        <v>156</v>
+        <v>23</v>
       </c>
       <c r="D83" s="38" t="s">
-        <v>157</v>
+        <v>74</v>
       </c>
       <c r="E83" s="38"/>
-      <c r="F83" s="38">
-        <v>119612606</v>
+      <c r="F83" s="38" t="s">
+        <v>153</v>
       </c>
       <c r="G83" s="38"/>
       <c r="H83" s="38"/>
@@ -2682,35 +2674,37 @@
     </row>
     <row r="84" spans="1:10" customHeight="1" ht="15">
       <c r="A84" s="38">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B84" s="38" t="s">
-        <v>48</v>
+        <v>154</v>
       </c>
       <c r="C84" s="38" t="s">
-        <v>49</v>
+        <v>155</v>
       </c>
       <c r="D84" s="38" t="s">
-        <v>50</v>
+        <v>156</v>
       </c>
       <c r="E84" s="38"/>
-      <c r="F84" s="38"/>
+      <c r="F84" s="38">
+        <v>119612606</v>
+      </c>
       <c r="G84" s="38"/>
       <c r="H84" s="38"/>
       <c r="I84" s="38"/>
     </row>
     <row r="85" spans="1:10" customHeight="1" ht="15">
       <c r="A85" s="38">
+        <v>58</v>
+      </c>
+      <c r="B85" s="38" t="s">
+        <v>58</v>
+      </c>
+      <c r="C85" s="38" t="s">
         <v>59</v>
       </c>
-      <c r="B85" s="38" t="s">
-        <v>48</v>
-      </c>
-      <c r="C85" s="38" t="s">
-        <v>49</v>
-      </c>
       <c r="D85" s="38" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="E85" s="38"/>
       <c r="F85" s="38"/>
@@ -2720,37 +2714,43 @@
     </row>
     <row r="86" spans="1:10" customHeight="1" ht="15">
       <c r="A86" s="38">
+        <v>59</v>
+      </c>
+      <c r="B86" s="38" t="s">
+        <v>58</v>
+      </c>
+      <c r="C86" s="38" t="s">
+        <v>59</v>
+      </c>
+      <c r="D86" s="38" t="s">
         <v>60</v>
       </c>
-      <c r="B86" s="38" t="s">
-        <v>22</v>
-      </c>
-      <c r="C86" s="38" t="s">
-        <v>26</v>
-      </c>
-      <c r="D86" s="38" t="s">
-        <v>146</v>
-      </c>
       <c r="E86" s="38"/>
-      <c r="F86" s="38" t="s">
-        <v>158</v>
-      </c>
+      <c r="F86" s="38"/>
       <c r="G86" s="38"/>
       <c r="H86" s="38"/>
       <c r="I86" s="38"/>
     </row>
     <row r="87" spans="1:10" customHeight="1" ht="15">
-      <c r="A87" s="22"/>
-      <c r="B87" s="22"/>
-      <c r="C87" s="22"/>
-      <c r="D87" s="22" t="s">
+      <c r="A87" s="38">
+        <v>60</v>
+      </c>
+      <c r="B87" s="38" t="s">
+        <v>157</v>
+      </c>
+      <c r="C87" s="38" t="s">
+        <v>23</v>
+      </c>
+      <c r="D87" s="38" t="s">
+        <v>158</v>
+      </c>
+      <c r="E87" s="38"/>
+      <c r="F87" s="38" t="s">
         <v>159</v>
       </c>
-      <c r="E87" s="22"/>
-      <c r="F87" s="22"/>
-      <c r="G87" s="22"/>
-      <c r="H87" s="22"/>
-      <c r="I87" s="22"/>
+      <c r="G87" s="38"/>
+      <c r="H87" s="38"/>
+      <c r="I87" s="38"/>
     </row>
     <row r="88" spans="1:10" customHeight="1" ht="15">
       <c r="A88" s="38">
@@ -2760,10 +2760,10 @@
         <v>160</v>
       </c>
       <c r="C88" s="38" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D88" s="38" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E88" s="38"/>
       <c r="F88" s="38" t="s">
@@ -2778,13 +2778,13 @@
         <v>62</v>
       </c>
       <c r="B89" s="38" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="C89" s="38" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D89" s="38" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E89" s="38"/>
       <c r="F89" s="38" t="s">
@@ -2799,13 +2799,13 @@
         <v>63</v>
       </c>
       <c r="B90" s="38" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="C90" s="38" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D90" s="38" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="E90" s="38"/>
       <c r="F90" s="38" t="s">
@@ -2820,10 +2820,10 @@
         <v>64</v>
       </c>
       <c r="B91" s="38" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="C91" s="38" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D91" s="38" t="s">
         <v>164</v>
@@ -2841,7 +2841,7 @@
         <v>65</v>
       </c>
       <c r="B92" s="38" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="C92" s="38" t="s">
         <v>166</v>
@@ -2872,7 +2872,7 @@
       </c>
       <c r="E93" s="38"/>
       <c r="F93" s="38" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="G93" s="38"/>
       <c r="H93" s="38"/>
@@ -3113,7 +3113,7 @@
       <c r="F112" s="2"/>
       <c r="G112" s="34" t="str">
         <f>C12</f>
-        <v>Coordinador de Operaciones</v>
+        <v>Coordinador Operaciones</v>
       </c>
       <c r="H112" s="34"/>
       <c r="I112" s="34"/>
